--- a/artfynd/A 31196-2023 artfynd.xlsx
+++ b/artfynd/A 31196-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31196-2023 artfynd.xlsx
+++ b/artfynd/A 31196-2023 artfynd.xlsx
@@ -3188,7 +3188,7 @@
         <v>117924557</v>
       </c>
       <c r="B23" t="n">
-        <v>78217</v>
+        <v>78219</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 31196-2023 artfynd.xlsx
+++ b/artfynd/A 31196-2023 artfynd.xlsx
@@ -3287,10 +3287,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118276597</v>
+        <v>118276596</v>
       </c>
       <c r="B24" t="n">
-        <v>91969</v>
+        <v>78220</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3303,21 +3303,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3327,10 +3327,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>545243</v>
+        <v>545253</v>
       </c>
       <c r="R24" t="n">
-        <v>7008814</v>
+        <v>7008817</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3393,10 +3393,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118276596</v>
+        <v>118276597</v>
       </c>
       <c r="B25" t="n">
-        <v>78220</v>
+        <v>91969</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3409,21 +3409,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3433,10 +3433,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>545253</v>
+        <v>545243</v>
       </c>
       <c r="R25" t="n">
-        <v>7008817</v>
+        <v>7008814</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 31196-2023 artfynd.xlsx
+++ b/artfynd/A 31196-2023 artfynd.xlsx
@@ -3605,10 +3605,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119846871</v>
+        <v>119846919</v>
       </c>
       <c r="B27" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3621,33 +3621,24 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skarflon, Skarflon, Jmt</t>
@@ -3716,10 +3707,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119846919</v>
+        <v>119846871</v>
       </c>
       <c r="B28" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3732,24 +3723,33 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skarflon, Skarflon, Jmt</t>

--- a/artfynd/A 31196-2023 artfynd.xlsx
+++ b/artfynd/A 31196-2023 artfynd.xlsx
@@ -3605,10 +3605,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119846919</v>
+        <v>119846871</v>
       </c>
       <c r="B27" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3621,24 +3621,33 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skarflon, Skarflon, Jmt</t>
@@ -3707,10 +3716,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119846871</v>
+        <v>119846919</v>
       </c>
       <c r="B28" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3723,33 +3732,24 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skarflon, Skarflon, Jmt</t>

--- a/artfynd/A 31196-2023 artfynd.xlsx
+++ b/artfynd/A 31196-2023 artfynd.xlsx
@@ -3605,10 +3605,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119846871</v>
+        <v>119846919</v>
       </c>
       <c r="B27" t="n">
-        <v>91832</v>
+        <v>91902</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3621,33 +3621,24 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skarflon, Skarflon, Jmt</t>
@@ -3716,10 +3707,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119846919</v>
+        <v>119846871</v>
       </c>
       <c r="B28" t="n">
-        <v>91884</v>
+        <v>91850</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3732,24 +3723,33 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skarflon, Skarflon, Jmt</t>

--- a/artfynd/A 31196-2023 artfynd.xlsx
+++ b/artfynd/A 31196-2023 artfynd.xlsx
@@ -3605,10 +3605,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119846919</v>
+        <v>119846871</v>
       </c>
       <c r="B27" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3621,24 +3621,33 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Skarflon, Skarflon, Jmt</t>
@@ -3707,10 +3716,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119846871</v>
+        <v>119846919</v>
       </c>
       <c r="B28" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3723,33 +3732,24 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Skarflon, Skarflon, Jmt</t>
